--- a/utils/monday_sprint_2023-t1.xlsx
+++ b/utils/monday_sprint_2023-t1.xlsx
@@ -87,7 +87,7 @@
     <t>17/03/2023</t>
   </si>
   <si>
-    <t>09/05/2026</t>
+    <t>04/05/2026</t>
   </si>
   <si>
     <t>Fila</t>
@@ -1025,7 +1025,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>18</v>

--- a/utils/monday_sprint_2023-t1.xlsx
+++ b/utils/monday_sprint_2023-t1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,51 +63,57 @@
     <t>19258</t>
   </si>
   <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Integração CRP e ERP</t>
+  </si>
+  <si>
+    <t>Bom dia, Segue abaixo chamado referente a integração entre o CRP e o ERP Altona. * Enviar o registro para o CRP no momento da criação da etiqueta (azul). Att,</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>06/04/2023</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>Fila</t>
+  </si>
+  <si>
+    <t>Aberto</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
     <t>2023-T1</t>
   </si>
   <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Integração CRP e ERP</t>
-  </si>
-  <si>
-    <t>Bom dia, Segue abaixo chamado referente a integração entre o CRP e o ERP Altona. * Enviar o registro para o CRP no momento da criação da etiqueta (azul). Att,</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>17/03/2023</t>
-  </si>
-  <si>
-    <t>09/05/2026</t>
-  </si>
-  <si>
-    <t>Fila</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
     <t>Base</t>
   </si>
   <si>
@@ -144,7 +153,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -169,6 +178,9 @@
   </si>
   <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -609,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -619,13 +631,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,49 +682,55 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -726,23 +746,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -750,16 +770,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -778,12 +798,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -791,7 +811,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -799,7 +819,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -817,7 +837,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -830,12 +850,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -859,54 +879,54 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -914,19 +934,19 @@
     </row>
     <row r="11" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -934,13 +954,19 @@
     </row>
     <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
+      <c r="J12" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
       <c r="M12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -948,13 +974,13 @@
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -962,13 +988,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -976,7 +1002,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -984,7 +1010,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -992,7 +1018,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1000,7 +1026,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -1011,24 +1037,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1144</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_2023-t1.xlsx
+++ b/utils/monday_sprint_2023-t1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -96,7 +96,7 @@
     <t>Fila</t>
   </si>
   <si>
-    <t>Aberto</t>
+    <t>Não</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -111,7 +111,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>2023-T1</t>
+    <t>Abr/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>Alta</t>
-  </si>
-  <si>
-    <t>Não</t>
   </si>
   <si>
     <t>A fazer</t>
@@ -837,7 +834,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -940,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="M11" t="s">
         <v>53</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
-        <v>54</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -960,13 +957,13 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="s">
         <v>55</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
-      </c>
-      <c r="M12" t="s">
-        <v>56</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -974,13 +971,13 @@
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="s">
         <v>57</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>58</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -988,7 +985,7 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1002,7 +999,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1018,7 +1015,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1026,10 +1023,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -1037,10 +1034,24 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1154</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_2023-t1.xlsx
+++ b/utils/monday_sprint_2023-t1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="143">
   <si>
     <t>Ticket</t>
   </si>
@@ -60,6 +60,9 @@
     <t>Mês</t>
   </si>
   <si>
+    <t>Origem</t>
+  </si>
+  <si>
     <t>19258</t>
   </si>
   <si>
@@ -87,22 +90,262 @@
     <t>Sistemas</t>
   </si>
   <si>
+    <t>17/03/2023</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>Fila</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Planejado</t>
+  </si>
+  <si>
+    <t>3877</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Melhorias</t>
+  </si>
+  <si>
+    <t>Movimentação de conjuntos já montados</t>
+  </si>
+  <si>
+    <t>Boa tarde Gentileza verificar a forma da realização da movimentação das peças para o deposito ser realizada por conjunto montado. Exemplo: Fornecemos a peça 2604710 para as Caterpillar. Porem a mesma peça é usada para a montagem do conjunto 3379543 e 3379544. É soldado um taquinho nas peças. A movim</t>
+  </si>
+  <si>
+    <t>NÃo definida</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>10/09/2020</t>
+  </si>
+  <si>
+    <t>20/04/2023</t>
+  </si>
+  <si>
+    <t>Fechado</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Fora da Sprint</t>
+  </si>
+  <si>
+    <t>18704</t>
+  </si>
+  <si>
+    <t>Setor nÃo informado</t>
+  </si>
+  <si>
+    <t>Erro no Sistema</t>
+  </si>
+  <si>
+    <t>Problema</t>
+  </si>
+  <si>
+    <t>Fluxo de ACVO Eletrônica</t>
+  </si>
+  <si>
+    <t>Bom dia, O fluxo de ACVO eletrônica, deve disparar os prazos e saldos de movimentação a todos os setores, de forma paralela. Por algum motivo, o sistema agora dispara movimentações individuais, ou seja, um processo não movimenta e nem enxerga a demanda sem o processo anterior movimentar - ou seja, e</t>
+  </si>
+  <si>
+    <t>Fernando Reinert</t>
+  </si>
+  <si>
+    <t>17/02/2023</t>
+  </si>
+  <si>
+    <t>13/04/2023</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>18795</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Inclusão no Planilhão MPS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor incluir no planilhão do MPS a data e hora que foi finalizado o processamento o planilhão. Servirá de ponto de corto para sabermos o que está pendente de apontamento de máquina. Atenciosamente, Caroline Schmitt Programadora de Produção | PCP Electro Aço Altona S.A. Rua Eng. Paul Wern</t>
+  </si>
+  <si>
+    <t>Caroline Schmitt</t>
+  </si>
+  <si>
+    <t>22/02/2023</t>
+  </si>
+  <si>
+    <t>18808</t>
+  </si>
+  <si>
+    <t>Tipos de OTF - Atrelar valor e peso em carteira.</t>
+  </si>
+  <si>
+    <t>Bom dia Sandro Conforme conversamos, precisamos atrelar valor e peso que aparece nas carteiras com o tipo da OTF cadastrada para não aparecer valores e pesos errados em carteira. Abaixo segue a lista de códigos criados e a situação de cada. As bases que devem constar que conheço são as abaixo. Carte</t>
+  </si>
+  <si>
+    <t>23/02/2023</t>
+  </si>
+  <si>
+    <t>11/04/2023</t>
+  </si>
+  <si>
+    <t>19109</t>
+  </si>
+  <si>
+    <t>ROMANEIO SISTEMA PORTARIA</t>
+  </si>
+  <si>
+    <t>Boa tarde, Abro um chamado para melhorar o procedimento de impressão de Romaneio no sistema da Portaria. O processo deve mudar pois se perde muito tempo na impressão de cada romaneio como segue abaixo: Primeiro no sistema da portaria venho em MANUTENÇÃO DE ROMANEIO E NA TELA ABAIXO BIPO A CHAVE DA N</t>
+  </si>
+  <si>
+    <t>Fabio Fernandes</t>
+  </si>
+  <si>
+    <t>09/03/2023</t>
+  </si>
+  <si>
+    <t>12/04/2023</t>
+  </si>
+  <si>
+    <t>19184</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>RES: Nova Coluna Planilhão (Produção seriada Bloqueada)</t>
+  </si>
+  <si>
+    <t>+@sistemas@ti-altona.movidesk.com Prezados, O chamado será priorizado. Abs, De: Samuel Garcia Enviada em: terça-feira, 14 de março de 2023 14:17 Para: Edson João Hammermeister Cc: Flavio Bett ; João Pedro Beccon ; Rafael Tamanini ; Cristiano Roberto Silva ; Delano Dallabrida ; Caroline Schmitt ; Cla</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>14/03/2023</t>
+  </si>
+  <si>
+    <t>19230</t>
+  </si>
+  <si>
+    <t>Gerar 2 relatórios diário</t>
+  </si>
+  <si>
+    <t>Bom dia gostaria que fosse gerado todo dia como o planilhão dois relatórios e fosse colocado junto com o arquivo MPS ou pode ser em outro arquivo. Carteira Geral de Pedidos - Sistema Carteira / Relatórios / Carteira Geral de pedidos Faturamento - Vendas / Relatórios / Relatórios Operacionais 2 / Not</t>
+  </si>
+  <si>
+    <t>Cristiano Roberto Silva</t>
+  </si>
+  <si>
+    <t>16/03/2023</t>
+  </si>
+  <si>
+    <t>19236</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>Campo obrigatório</t>
+  </si>
+  <si>
+    <t>Boa tarde, Conforme o último chamado, esqueci de pontuar para deixar esse campo de preenchimento do tempo de desmoldagem obrigatório. Sendo assim, a melhor opção seria "a partir de x horas". Obrigada!</t>
+  </si>
+  <si>
+    <t>Julia Prebianca</t>
+  </si>
+  <si>
     <t>06/04/2023</t>
   </si>
   <si>
-    <t>04/05/2026</t>
-  </si>
-  <si>
-    <t>Fila</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
-    <t>Abril</t>
+    <t>19268</t>
+  </si>
+  <si>
+    <t>BOTÃO PARA SELECIONAR OS CONTATOS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de abrir um chamado para criação de um botão "selecionar todos" nos e-mails das ordens de compra, tanto no SIC WEB quando na ordem de compra padrão. Fico no aguardo. At.</t>
+  </si>
+  <si>
+    <t>Cristian Rafael de Azevedo</t>
+  </si>
+  <si>
+    <t>19343</t>
+  </si>
+  <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>Tela de programação - modelação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugestão de algumas melhorias: OBS.: TODOS OS ITENS JÁ IMPORTADOS PODEM SER EXCLUÍDOS. A PROGRAMAÇÃO AINDA É FEITA MANUALMENTE E NO SISTEMA FIZ ALGUMAS MUDANÇAS APENAS PARA TSTE. 1º - Permitir que os prazos para os consertos possam ser alterados pelos seguintes cadastros, 143415, 115270, 132550. 2º </t>
+  </si>
+  <si>
+    <t>Guilherme Barcelos</t>
+  </si>
+  <si>
+    <t>22/03/2023</t>
+  </si>
+  <si>
+    <t>19365</t>
+  </si>
+  <si>
+    <t>AMOSTRA ALTO IMPACTO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor adicionar um novo tipo de produção "AMOSTRA ALTO IMPACTO" na tela do CPP conforme imagem abaixo. At.te</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
+    <t>19543</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>alterações na tela de movimentação setorial</t>
+  </si>
+  <si>
+    <t>Boa tarde, Por gentileza alterar o seguinte na tela de movimentação setorial "demais setores": - adicionar a coluna "retrabalho" (igual ao fluxo de produção, conforme último print) - mudar a ordem das colunas, mantendo as duas primeiras e inserindo após: OTF, Cód. Cliente, Razão Social Obrigada! Lau</t>
+  </si>
+  <si>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>Dashboard de Change Log - Governança de TI</t>
@@ -111,7 +354,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>Abr/2023</t>
+    <t>06/04/2023 a 20/04/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -123,7 +366,7 @@
     <t>Total de tickets</t>
   </si>
   <si>
-    <t>% dentro do SLA</t>
+    <t>% planejado</t>
   </si>
   <si>
     <t>Tempo médio (dias)</t>
@@ -153,7 +396,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA (15 dias)</t>
+    <t>Planejado x Fora da Sprint</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -168,9 +411,6 @@
     <t>Muito Alta</t>
   </si>
   <si>
-    <t>Sim</t>
-  </si>
-  <si>
     <t>Alta</t>
   </si>
   <si>
@@ -198,7 +438,7 @@
     <t>Em Análise</t>
   </si>
   <si>
-    <t>Top tickets fora do SLA</t>
+    <t>Demandas atendidas fora da sprint</t>
   </si>
   <si>
     <t>Atraso (dias)</t>
@@ -618,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -634,9 +874,10 @@
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,52 +923,658 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>29</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -743,23 +1590,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>30</v>
+        <v>111</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>115</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -767,16 +1614,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>38</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -795,12 +1642,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>39</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -808,7 +1655,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -816,7 +1663,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -834,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -847,12 +1694,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>43</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -876,54 +1723,54 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>131</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -931,19 +1778,19 @@
     </row>
     <row r="11" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G11" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M11" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -951,19 +1798,19 @@
     </row>
     <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -971,13 +1818,13 @@
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -985,13 +1832,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -999,7 +1846,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -1007,7 +1854,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N16">
         <v>1</v>
@@ -1015,7 +1862,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -1023,7 +1870,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>61</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.25">
@@ -1034,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -1042,16 +1889,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F21" s="2">
-        <v>1154</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
